--- a/data-raw/MST.xlsx
+++ b/data-raw/MST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/MST/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B21DD1F-B8E5-3840-8DF4-B6334282EC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D6689D-6689-6341-9946-DD71D42E3E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1060" windowWidth="35840" windowHeight="19200" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
   </bookViews>
@@ -47,15 +47,6 @@
     <t>Welcome to the Melody Singing Task!</t>
   </si>
   <si>
-    <t xml:space="preserve">We advise that you sing with a "Daah" sound. </t>
-  </si>
-  <si>
-    <t>Try not to "wobble" or "vibrato" your notes when you sing: try and produce notes which are as stable as possible.</t>
-  </si>
-  <si>
-    <t>Sing towards your microphone, not too far away from it. About the length of a 30cm ruler is good.</t>
-  </si>
-  <si>
     <t>When you click the Play button in the next set of trials, you will hear a 5-second note</t>
   </si>
   <si>
@@ -122,7 +113,16 @@
     <t>Please read the instructions carefully.</t>
   </si>
   <si>
-    <t>In this task we’ll ask you to sing back a few notes and melodies that we play to you. It is fine if you think you are not a good singer. The test will start easy and get very hard. Just do your best and have fun!</t>
+    <t xml:space="preserve">In this task we’ll ask you to sing back a few notes and melodies that we play to you. It is fine if you think you are not a good singer. Throughout this first singing test, you will probably find some examples easy and others harder, and in general, as this specific singing test progresses, the trials become more challenging. Just always make your best attempt.” </t>
+  </si>
+  <si>
+    <t>Sing towards your microphone, not too far away from it. About the length of a 30cm (12 inch) ruler is good.</t>
+  </si>
+  <si>
+    <t>You will be asked to imitate some sounds.  Please sing these notes back on the syllable "daah"   as in  the first part of the word  “dog” [rhymes with “fa la la”. ].</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Try to produce notes that are as stable as possible, without vibrato. That is, try note to wobble  your notes.  The computer can analyse a “straight” sound best. </t>
   </si>
 </sst>
 </file>
@@ -213,7 +213,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -548,7 +548,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>3</v>
@@ -556,71 +556,71 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>0</v>
@@ -628,34 +628,34 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">

--- a/data-raw/MST.xlsx
+++ b/data-raw/MST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/MST/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D6689D-6689-6341-9946-DD71D42E3E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB6E13D-9FB0-D448-ADF9-9FBECA5AA36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1060" windowWidth="35840" windowHeight="19200" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
   </bookViews>
@@ -113,9 +113,6 @@
     <t>Please read the instructions carefully.</t>
   </si>
   <si>
-    <t xml:space="preserve">In this task we’ll ask you to sing back a few notes and melodies that we play to you. It is fine if you think you are not a good singer. Throughout this first singing test, you will probably find some examples easy and others harder, and in general, as this specific singing test progresses, the trials become more challenging. Just always make your best attempt.” </t>
-  </si>
-  <si>
     <t>Sing towards your microphone, not too far away from it. About the length of a 30cm (12 inch) ruler is good.</t>
   </si>
   <si>
@@ -123,6 +120,9 @@
   </si>
   <si>
     <t xml:space="preserve"> Try to produce notes that are as stable as possible, without vibrato. That is, try note to wobble  your notes.  The computer can analyse a “straight” sound best. </t>
+  </si>
+  <si>
+    <t>In this task we’ll ask you to sing back a few notes and melodies that we play to you. It is fine if you think you are not a good singer. Throughout this first singing test, you will probably find some examples easy and others harder, and in general, as this specific singing test progresses, the trials become more challenging. Just always make your best attempt.</t>
   </si>
 </sst>
 </file>
@@ -559,7 +559,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -583,7 +583,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -591,7 +591,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -599,7 +599,7 @@
         <v>22</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
